--- a/misc/keymap.xlsx
+++ b/misc/keymap.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="215">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -418,6 +418,24 @@
   </si>
   <si>
     <t xml:space="preserve">A+F11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マウスモード</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左クリック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">右クリック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhlUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhlDn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back</t>
   </si>
   <si>
     <t xml:space="preserve">標準(レジストリ編集)</t>
@@ -658,7 +676,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="游ゴシック"/>
@@ -697,6 +715,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="7"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -926,6 +950,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -934,7 +962,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -952,10 +980,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2439,51 +2463,23 @@
       <c r="O2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y2" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="Q2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -2529,48 +2525,26 @@
         <v>19</v>
       </c>
       <c r="O3" s="2"/>
-      <c r="Q3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2615,45 +2589,27 @@
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="Q4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="2"/>
       <c r="W4" s="2" t="s">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>28</v>
+        <v>53</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC4" s="2" t="s">
-        <v>32</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
     </row>
@@ -2699,45 +2655,23 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="Q5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>39</v>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
     </row>
@@ -2777,39 +2711,19 @@
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
-      <c r="Q6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
       <c r="Z6" s="6"/>
-      <c r="AA6" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="AA6" s="2"/>
       <c r="AB6" s="6"/>
-      <c r="AC6" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="AC6" s="2"/>
       <c r="AD6" s="6"/>
       <c r="AE6" s="6"/>
     </row>
@@ -2846,37 +2760,31 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="6"/>
       <c r="AA7" s="2"/>
-      <c r="AB7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2893,7 +2801,7 @@
       <c r="N9" s="12"/>
       <c r="O9" s="13"/>
       <c r="Q9" s="7" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
@@ -2958,36 +2866,36 @@
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
@@ -3038,37 +2946,37 @@
       <c r="O11" s="2"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB11" s="16" t="s">
-        <v>153</v>
+        <v>158</v>
+      </c>
+      <c r="AB11" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="AC11" s="10" t="s">
         <v>93</v>
@@ -3120,37 +3028,37 @@
       <c r="O12" s="2"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AB12" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AC12" s="10" t="s">
         <v>94</v>
@@ -3202,37 +3110,37 @@
       <c r="O13" s="2"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -3330,24 +3238,24 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -3363,10 +3271,10 @@
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
       <c r="O17" s="13"/>
-      <c r="Q17" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="R17" s="17"/>
+      <c r="Q17" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="R17" s="18"/>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
       <c r="U17" s="12"/>
@@ -3383,7 +3291,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>109</v>
@@ -3491,7 +3399,7 @@
       <c r="X19" s="2"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
@@ -3516,7 +3424,7 @@
         <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>87</v>
@@ -3548,14 +3456,14 @@
       <c r="U20" s="4"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Y20" s="3"/>
       <c r="Z20" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
@@ -3589,7 +3497,7 @@
         <v>54</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="2"/>
@@ -3606,7 +3514,7 @@
       <c r="U21" s="2"/>
       <c r="V21" s="3"/>
       <c r="W21" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="X21" s="2"/>
       <c r="Y21" s="3"/>
@@ -3701,26 +3609,26 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="15"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="17"/>
+        <v>191</v>
+      </c>
+      <c r="B25" s="18"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
@@ -3737,10 +3645,10 @@
       <c r="P25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q25" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="R25" s="17"/>
+      <c r="Q25" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="R25" s="18"/>
       <c r="S25" s="12"/>
       <c r="T25" s="12"/>
       <c r="U25" s="12"/>
@@ -3859,13 +3767,13 @@
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
@@ -3888,7 +3796,7 @@
         <v>85</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>87</v>
@@ -3922,16 +3830,16 @@
       <c r="U28" s="4"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
@@ -3965,7 +3873,7 @@
         <v>54</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="2"/>
@@ -3982,10 +3890,10 @@
       <c r="U29" s="2"/>
       <c r="V29" s="3"/>
       <c r="W29" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="Y29" s="3"/>
       <c r="Z29" s="2"/>
@@ -4081,24 +3989,24 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="15"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
-      <c r="B33" s="17"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
@@ -4113,9 +4021,9 @@
       <c r="N33" s="12"/>
       <c r="O33" s="13"/>
       <c r="Q33" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="R33" s="17"/>
+        <v>195</v>
+      </c>
+      <c r="R33" s="18"/>
       <c r="S33" s="12"/>
       <c r="T33" s="12"/>
       <c r="U33" s="12"/>
@@ -4255,7 +4163,7 @@
       <c r="Q35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="R35" s="19" t="s">
+      <c r="R35" s="20" t="s">
         <v>74</v>
       </c>
       <c r="S35" s="3" t="s">
@@ -4270,25 +4178,25 @@
       <c r="V35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="W35" s="19" t="s">
+      <c r="W35" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="X35" s="19" t="s">
+      <c r="X35" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="Y35" s="19" t="s">
+      <c r="Y35" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="Z35" s="19" t="s">
+      <c r="Z35" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AA35" s="19" t="s">
+      <c r="AA35" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="AB35" s="19" t="s">
+      <c r="AB35" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="AC35" s="19" t="s">
+      <c r="AC35" s="20" t="s">
         <v>79</v>
       </c>
       <c r="AD35" s="2"/>
@@ -4309,7 +4217,7 @@
         <v>85</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>87</v>
@@ -4337,10 +4245,10 @@
       <c r="Q36" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="R36" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="S36" s="19" t="s">
+      <c r="R36" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="S36" s="20" t="s">
         <v>83</v>
       </c>
       <c r="T36" s="3" t="s">
@@ -4349,28 +4257,28 @@
       <c r="U36" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="V36" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="W36" s="19" t="s">
+      <c r="V36" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="W36" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="X36" s="19" t="s">
+      <c r="X36" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="Y36" s="19" t="s">
+      <c r="Y36" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="Z36" s="19" t="s">
+      <c r="Z36" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AA36" s="19" t="s">
+      <c r="AA36" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="AB36" s="19" t="s">
+      <c r="AB36" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="AC36" s="19" t="s">
+      <c r="AC36" s="20" t="s">
         <v>80</v>
       </c>
       <c r="AD36" s="2"/>
@@ -4402,10 +4310,10 @@
         <v>54</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -4420,22 +4328,22 @@
       <c r="R37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S37" s="19" t="s">
+      <c r="S37" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="T37" s="19" t="s">
+      <c r="T37" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="U37" s="19" t="s">
+      <c r="U37" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="V37" s="19" t="s">
+      <c r="V37" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="W37" s="19" t="s">
+      <c r="W37" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="X37" s="19" t="s">
+      <c r="X37" s="20" t="s">
         <v>54</v>
       </c>
       <c r="Y37" s="3"/>
@@ -4555,26 +4463,26 @@
       <c r="AE39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="18"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="15"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B41" s="17"/>
+      <c r="A41" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="18"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
@@ -4588,10 +4496,10 @@
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
       <c r="O41" s="13"/>
-      <c r="Q41" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="R41" s="17"/>
+      <c r="Q41" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="R41" s="18"/>
       <c r="S41" s="12"/>
       <c r="T41" s="12"/>
       <c r="U41" s="12"/>
@@ -4649,7 +4557,7 @@
       <c r="H43" s="2"/>
       <c r="I43" s="3"/>
       <c r="J43" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -4658,7 +4566,7 @@
       <c r="O43" s="2"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
@@ -4666,14 +4574,14 @@
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
       <c r="X43" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AB43" s="2"/>
       <c r="AC43" s="2"/>
@@ -4692,14 +4600,14 @@
       <c r="E44" s="4"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -4719,7 +4627,7 @@
       <c r="W44" s="2"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
@@ -4736,7 +4644,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="3"/>
       <c r="G45" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="3"/>
@@ -4758,15 +4666,15 @@
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="2"/>
-      <c r="AA45" s="20" t="s">
+      <c r="AA45" s="21" t="s">
         <v>43</v>
       </c>
       <c r="AB45" s="2"/>
@@ -4855,27 +4763,27 @@
       <c r="AE47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="15"/>
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="B49" s="17"/>
+      <c r="A49" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B49" s="18"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
       <c r="E49" s="12"/>
@@ -4889,8 +4797,8 @@
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
       <c r="O49" s="13"/>
-      <c r="Q49" s="21" t="s">
-        <v>205</v>
+      <c r="Q49" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5024,7 +4932,7 @@
         <v>19</v>
       </c>
       <c r="AC51" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AD51" s="2"/>
       <c r="AE51" s="2"/>
@@ -5032,37 +4940,37 @@
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="M52" s="10" t="s">
         <v>94</v>
@@ -5088,13 +4996,13 @@
         <v>3</v>
       </c>
       <c r="AA52" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AC52" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AD52" s="2"/>
       <c r="AE52" s="2"/>
@@ -5119,22 +5027,22 @@
         <v>81</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>33</v>
@@ -5185,10 +5093,10 @@
         <v>49</v>
       </c>
       <c r="G54" s="3"/>
-      <c r="H54" s="20" t="s">
+      <c r="H54" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I54" s="20" t="s">
+      <c r="I54" s="21" t="s">
         <v>58</v>
       </c>
       <c r="J54" s="6"/>
@@ -5223,8 +5131,8 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
       <c r="J55" s="6"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -5840,24 +5748,24 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -6114,24 +6022,24 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -6288,7 +6196,7 @@
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>33</v>
@@ -6355,26 +6263,26 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="15"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="17"/>
+        <v>191</v>
+      </c>
+      <c r="B25" s="18"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
@@ -6436,13 +6344,13 @@
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="20" t="s">
         <v>52</v>
       </c>
       <c r="J27" s="2" t="s">
@@ -6460,34 +6368,34 @@
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="J28" s="19" t="s">
+      <c r="J28" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="K28" s="19" t="s">
+      <c r="K28" s="20" t="s">
         <v>19</v>
       </c>
       <c r="L28" s="2"/>
@@ -6502,19 +6410,19 @@
       <c r="B29" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="20" t="s">
         <v>92</v>
       </c>
       <c r="H29" s="22" t="s">
@@ -6528,7 +6436,7 @@
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>33</v>
@@ -6588,26 +6496,26 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="15"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B33" s="17"/>
+        <v>212</v>
+      </c>
+      <c r="B33" s="18"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
@@ -6707,37 +6615,37 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>94</v>
@@ -6783,7 +6691,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>18</v>
@@ -6804,16 +6712,16 @@
         <v>2</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>33</v>
@@ -6874,10 +6782,10 @@
         <v>49</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="20" t="s">
+      <c r="H38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I38" s="20" t="s">
+      <c r="I38" s="21" t="s">
         <v>58</v>
       </c>
       <c r="J38" s="6"/>
@@ -6897,8 +6805,8 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
       <c r="J39" s="6"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -6907,26 +6815,26 @@
       <c r="O39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="18"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="15"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B41" s="17"/>
+        <v>213</v>
+      </c>
+      <c r="B41" s="18"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
@@ -7134,27 +7042,27 @@
       <c r="O47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="15"/>
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B49" s="17"/>
+      <c r="A49" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B49" s="18"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
       <c r="E49" s="12"/>
@@ -7213,14 +7121,14 @@
       <c r="E52" s="4"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -7236,7 +7144,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="3"/>
       <c r="G53" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="3"/>

--- a/misc/keymap.xlsx
+++ b/misc/keymap.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="space modifier" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="space modifier_2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="space modifier_2_2" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="space modifier" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="space modifier_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="space modifier_2_2" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="217">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -429,6 +429,9 @@
     <t xml:space="preserve">右クリック</t>
   </si>
   <si>
+    <t xml:space="preserve">Norml</t>
+  </si>
+  <si>
     <t xml:space="preserve">WhlUp</t>
   </si>
   <si>
@@ -438,6 +441,12 @@
     <t xml:space="preserve">Back</t>
   </si>
   <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next</t>
+  </si>
+  <si>
     <t xml:space="preserve">標準(レジストリ編集)</t>
   </si>
   <si>
@@ -573,9 +582,6 @@
     <t xml:space="preserve">F13修飾</t>
   </si>
   <si>
-    <t xml:space="preserve">無変換 修飾</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reload</t>
   </si>
   <si>
@@ -594,6 +600,9 @@
     <t xml:space="preserve">Num</t>
   </si>
   <si>
+    <t xml:space="preserve">Mouse</t>
+  </si>
+  <si>
     <t xml:space="preserve">S+End</t>
   </si>
   <si>
@@ -615,9 +624,6 @@
     <t xml:space="preserve">Space &amp; F13 修飾</t>
   </si>
   <si>
-    <t xml:space="preserve">APP</t>
-  </si>
-  <si>
     <t xml:space="preserve">/ 修飾   C+k,C+{}</t>
   </si>
   <si>
@@ -657,7 +663,7 @@
     <t xml:space="preserve"> (F14 or 変換 or 無変換) 修飾</t>
   </si>
   <si>
-    <t xml:space="preserve">Lock</t>
+    <t xml:space="preserve">Layer1</t>
   </si>
   <si>
     <t xml:space="preserve">ひらがな./変換/無変換　修飾</t>
@@ -1058,6 +1064,112 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -2535,8 +2647,8 @@
       <c r="X3" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="Y3" s="3" t="n">
-        <v>5</v>
+      <c r="Y3" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="Z3" s="14" t="s">
         <v>134</v>
@@ -2589,14 +2701,16 @@
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="Q4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="4"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="X4" s="4" t="s">
         <v>53</v>
@@ -2662,10 +2776,10 @@
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
@@ -2716,14 +2830,18 @@
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="V6" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="6"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="6"/>
-      <c r="AC6" s="2"/>
+      <c r="AC6" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="AD6" s="6"/>
       <c r="AE6" s="6"/>
     </row>
@@ -2760,9 +2878,15 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="6"/>
       <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
+      <c r="AB7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="AE7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2784,7 +2908,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2801,7 +2925,7 @@
       <c r="N9" s="12"/>
       <c r="O9" s="13"/>
       <c r="Q9" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
@@ -2866,36 +2990,36 @@
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
@@ -2946,37 +3070,37 @@
       <c r="O11" s="2"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AB11" s="17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AC11" s="10" t="s">
         <v>93</v>
@@ -3028,37 +3152,37 @@
       <c r="O12" s="2"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AB12" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AC12" s="10" t="s">
         <v>94</v>
@@ -3110,37 +3234,37 @@
       <c r="O13" s="2"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -3255,7 +3379,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -3271,9 +3395,7 @@
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
       <c r="O17" s="13"/>
-      <c r="Q17" s="18" t="s">
-        <v>183</v>
-      </c>
+      <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
@@ -3291,7 +3413,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>109</v>
@@ -3399,7 +3521,7 @@
       <c r="X19" s="2"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
@@ -3424,7 +3546,7 @@
         <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>87</v>
@@ -3456,14 +3578,14 @@
       <c r="U20" s="4"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Y20" s="3"/>
       <c r="Z20" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
@@ -3497,9 +3619,11 @@
         <v>54</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J21" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2" t="s">
@@ -3514,7 +3638,7 @@
       <c r="U21" s="2"/>
       <c r="V21" s="3"/>
       <c r="W21" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="X21" s="2"/>
       <c r="Y21" s="3"/>
@@ -3626,7 +3750,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="12"/>
@@ -3646,7 +3770,7 @@
         <v>42</v>
       </c>
       <c r="Q25" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="R25" s="18"/>
       <c r="S25" s="12"/>
@@ -3767,13 +3891,13 @@
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
@@ -3796,7 +3920,7 @@
         <v>85</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>87</v>
@@ -3830,16 +3954,16 @@
       <c r="U28" s="4"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="X28" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z28" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="X28" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y28" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z28" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
@@ -3873,9 +3997,11 @@
         <v>54</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J29" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2" t="s">
@@ -3890,10 +4016,10 @@
       <c r="U29" s="2"/>
       <c r="V29" s="3"/>
       <c r="W29" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y29" s="3"/>
       <c r="Z29" s="2"/>
@@ -4021,7 +4147,7 @@
       <c r="N33" s="12"/>
       <c r="O33" s="13"/>
       <c r="Q33" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="12"/>
@@ -4217,7 +4343,7 @@
         <v>85</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>87</v>
@@ -4246,7 +4372,7 @@
         <v>57</v>
       </c>
       <c r="R36" s="20" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S36" s="20" t="s">
         <v>83</v>
@@ -4258,7 +4384,7 @@
         <v>85</v>
       </c>
       <c r="V36" s="20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="W36" s="20" t="s">
         <v>87</v>
@@ -4309,12 +4435,8 @@
       <c r="H37" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>197</v>
-      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2" t="s">
@@ -4370,9 +4492,7 @@
         <v>47</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="2" t="s">
         <v>1</v>
@@ -4480,7 +4600,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="12"/>
@@ -4497,7 +4617,7 @@
       <c r="N41" s="12"/>
       <c r="O41" s="13"/>
       <c r="Q41" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="12"/>
@@ -4557,7 +4677,7 @@
       <c r="H43" s="2"/>
       <c r="I43" s="3"/>
       <c r="J43" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -4566,7 +4686,7 @@
       <c r="O43" s="2"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
@@ -4574,20 +4694,18 @@
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
       <c r="X43" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AB43" s="2"/>
       <c r="AC43" s="2"/>
-      <c r="AD43" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="AD43" s="2"/>
       <c r="AE43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4600,14 +4718,14 @@
       <c r="E44" s="4"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -4627,7 +4745,7 @@
       <c r="W44" s="2"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
@@ -4644,7 +4762,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="3"/>
       <c r="G45" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="3"/>
@@ -4654,9 +4772,7 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
-      <c r="Q45" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
         <v>89</v>
@@ -4666,10 +4782,10 @@
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
@@ -4678,9 +4794,7 @@
         <v>43</v>
       </c>
       <c r="AB45" s="2"/>
-      <c r="AC45" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" s="2"/>
       <c r="AE45" s="2"/>
     </row>
@@ -4702,29 +4816,17 @@
       <c r="M46" s="2"/>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
-      <c r="Q46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
       <c r="U46" s="3"/>
-      <c r="V46" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="V46" s="3"/>
       <c r="W46" s="3"/>
       <c r="X46" s="2"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6"/>
-      <c r="AA46" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="AA46" s="2"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="6"/>
@@ -4781,7 +4883,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="12"/>
@@ -4798,7 +4900,7 @@
       <c r="N49" s="12"/>
       <c r="O49" s="13"/>
       <c r="Q49" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4932,7 +5034,7 @@
         <v>19</v>
       </c>
       <c r="AC51" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AD51" s="2"/>
       <c r="AE51" s="2"/>
@@ -4940,44 +5042,46 @@
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M52" s="10" t="s">
         <v>94</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
-      <c r="Q52" s="3"/>
+      <c r="Q52" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
@@ -4996,13 +5100,13 @@
         <v>3</v>
       </c>
       <c r="AA52" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AC52" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AD52" s="2"/>
       <c r="AE52" s="2"/>
@@ -5027,22 +5131,22 @@
         <v>81</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>33</v>
@@ -5077,9 +5181,7 @@
       <c r="A54" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
         <v>46</v>
       </c>
@@ -5089,9 +5191,7 @@
       <c r="E54" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="21" t="s">
         <v>50</v>
@@ -5112,7 +5212,9 @@
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
+      <c r="V54" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
@@ -5765,7 +5867,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -6039,7 +6141,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -6196,7 +6298,7 @@
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>33</v>
@@ -6280,7 +6382,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="12"/>
@@ -6436,7 +6538,7 @@
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>33</v>
@@ -6513,7 +6615,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="12"/>
@@ -6615,37 +6717,37 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>94</v>
@@ -6691,7 +6793,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>18</v>
@@ -6712,16 +6814,16 @@
         <v>2</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>33</v>
@@ -6832,7 +6934,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="12"/>
@@ -7060,7 +7162,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="12"/>
@@ -7121,14 +7223,14 @@
       <c r="E52" s="4"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -7144,7 +7246,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="3"/>
       <c r="G53" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="3"/>

--- a/misc/keymap.xlsx
+++ b/misc/keymap.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="long_press_shift(JP)" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="long_press_shift(US)" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="long_press_shift(US)_2" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="203">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -251,6 +252,12 @@
     <t xml:space="preserve">)</t>
   </si>
   <si>
+    <t xml:space="preserve">=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~</t>
+  </si>
+  <si>
     <t xml:space="preserve">|</t>
   </si>
   <si>
@@ -614,7 +621,10 @@
     <t xml:space="preserve">S+F12</t>
   </si>
   <si>
-    <t xml:space="preserve">=</t>
+    <t xml:space="preserve">US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP</t>
   </si>
   <si>
     <t xml:space="preserve">＼</t>
@@ -1644,11 +1654,15 @@
         <v>75</v>
       </c>
       <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
+      <c r="AB10" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="AC10" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD10" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="AE10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1697,47 +1711,47 @@
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Y11" s="7" t="s">
         <v>16</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AA11" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AB11" s="14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AC11" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>26</v>
@@ -1779,40 +1793,40 @@
       <c r="O12" s="6"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W12" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y12" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AC12" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AD12" s="6"/>
       <c r="AE12" s="6"/>
@@ -1861,37 +1875,37 @@
       <c r="O13" s="6"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AB13" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
@@ -1921,7 +1935,7 @@
         <v>61</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="6" t="s">
@@ -2006,7 +2020,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2040,43 +2054,43 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
@@ -2098,25 +2112,25 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>6</v>
@@ -2134,7 +2148,7 @@
         <v>21</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
@@ -2148,7 +2162,7 @@
       <c r="X19" s="6"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
@@ -2158,25 +2172,25 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>40</v>
@@ -2191,10 +2205,10 @@
         <v>21</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -2205,14 +2219,14 @@
       <c r="U20" s="9"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
@@ -2225,31 +2239,31 @@
         <v>43</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
@@ -2265,7 +2279,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="7"/>
       <c r="W21" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
@@ -2377,7 +2391,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="4"/>
@@ -2397,7 +2411,7 @@
         <v>7</v>
       </c>
       <c r="Q25" s="16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R25" s="16"/>
       <c r="S25" s="4"/>
@@ -2417,40 +2431,40 @@
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -2473,22 +2487,22 @@
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>6</v>
@@ -2506,7 +2520,7 @@
         <v>21</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
@@ -2518,13 +2532,13 @@
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
       <c r="X27" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Y27" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Z27" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA27" s="6"/>
       <c r="AB27" s="6"/>
@@ -2535,22 +2549,22 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>40</v>
@@ -2565,15 +2579,15 @@
         <v>21</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
       <c r="Q28" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
@@ -2581,16 +2595,16 @@
       <c r="U28" s="9"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Y28" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Z28" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
@@ -2603,31 +2617,31 @@
         <v>43</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="G29" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
@@ -2643,10 +2657,10 @@
       <c r="U29" s="6"/>
       <c r="V29" s="7"/>
       <c r="W29" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X29" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Y29" s="7"/>
       <c r="Z29" s="6"/>
@@ -2774,7 +2788,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="R33" s="16"/>
       <c r="S33" s="4"/>
@@ -2794,40 +2808,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M34" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -2835,40 +2849,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB34" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC34" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -2876,22 +2890,22 @@
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>6</v>
@@ -2909,7 +2923,7 @@
         <v>21</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
@@ -2917,22 +2931,22 @@
         <v>8</v>
       </c>
       <c r="R35" s="19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="V35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="W35" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X35" s="19" t="s">
         <v>6</v>
@@ -2950,7 +2964,7 @@
         <v>21</v>
       </c>
       <c r="AC35" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
@@ -2958,22 +2972,22 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>40</v>
@@ -2988,33 +3002,33 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="Q36" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R36" s="19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="S36" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="V36" s="19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="W36" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="X36" s="19" t="s">
         <v>40</v>
@@ -3029,10 +3043,10 @@
         <v>21</v>
       </c>
       <c r="AB36" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AC36" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -3042,22 +3056,22 @@
         <v>43</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D37" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="G37" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>41</v>
@@ -3075,22 +3089,22 @@
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="S37" s="19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T37" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="U37" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="V37" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="U37" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="V37" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="W37" s="19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X37" s="19" t="s">
         <v>41</v>
@@ -3158,7 +3172,7 @@
         <v>61</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z38" s="11"/>
       <c r="AA38" s="6" t="s">
@@ -3227,7 +3241,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="4"/>
@@ -3244,7 +3258,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R41" s="16"/>
       <c r="S41" s="4"/>
@@ -3304,7 +3318,7 @@
       <c r="H43" s="6"/>
       <c r="I43" s="7"/>
       <c r="J43" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
@@ -3313,7 +3327,7 @@
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -3321,14 +3335,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -3337,7 +3351,7 @@
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -3345,14 +3359,14 @@
       <c r="E44" s="9"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
@@ -3362,17 +3376,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
       <c r="X44" s="9"/>
       <c r="Y44" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -3389,7 +3403,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
@@ -3402,17 +3416,17 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -3510,7 +3524,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="4"/>
@@ -3527,46 +3541,46 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
@@ -3599,40 +3613,40 @@
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M51" s="15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -3643,7 +3657,7 @@
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X51" s="6" t="n">
         <v>4</v>
@@ -3696,13 +3710,13 @@
         <v>75</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L52" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M52" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
@@ -3727,10 +3741,10 @@
         <v>3</v>
       </c>
       <c r="AA52" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AB52" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>75</v>
@@ -3749,31 +3763,31 @@
         <v>37</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>3</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>43</v>
@@ -3824,7 +3838,7 @@
         <v>61</v>
       </c>
       <c r="I54" s="20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J54" s="11"/>
       <c r="K54" s="6" t="s">
@@ -4223,7 +4237,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4240,7 +4254,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="5"/>
       <c r="Q1" s="3" t="s">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -4259,7 +4273,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>1</v>
@@ -4295,7 +4309,7 @@
         <v>3</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>6</v>
@@ -4303,23 +4317,51 @@
       <c r="O2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="X2" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
+      <c r="Y2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -4362,29 +4404,51 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O3" s="6"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
+      <c r="Q3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="AE3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4432,28 +4496,44 @@
       </c>
       <c r="O4" s="6"/>
       <c r="Q4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="W4" s="6" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y4" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="AD4" s="6"/>
       <c r="AE4" s="6"/>
     </row>
@@ -4492,30 +4572,52 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="6" t="s">
-        <v>53</v>
+      <c r="Q5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
     </row>
@@ -4570,7 +4672,7 @@
         <v>58</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>60</v>
@@ -4579,18 +4681,16 @@
       <c r="X6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Y6" s="7" t="s">
+      <c r="Y6" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="Z6" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="Z6" s="11"/>
       <c r="AA6" s="6" t="s">
         <v>55</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
@@ -4626,16 +4726,16 @@
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
+      <c r="Z7" s="11"/>
       <c r="AA7" s="6"/>
-      <c r="AB7" s="7" t="s">
-        <v>54</v>
+      <c r="AB7" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="AD7" s="6" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="AE7" s="6"/>
     </row>
@@ -4694,7 +4794,7 @@
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>1</v>
@@ -4730,7 +4830,7 @@
         <v>3</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="N10" s="6" t="s">
         <v>6</v>
@@ -4761,7 +4861,7 @@
         <v>72</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Z10" s="7" t="s">
         <v>74</v>
@@ -4770,10 +4870,10 @@
         <v>75</v>
       </c>
       <c r="AB10" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AC10" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AD10" s="6"/>
       <c r="AE10" s="6" t="s">
@@ -4821,54 +4921,54 @@
         <v>37</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Y11" s="7" t="s">
         <v>16</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AA11" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AB11" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AD11" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AE11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>26</v>
@@ -4901,7 +5001,7 @@
         <v>35</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>21</v>
@@ -4912,31 +5012,31 @@
       <c r="O12" s="6"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W12" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y12" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA12" s="6" t="s">
         <v>36</v>
@@ -4985,7 +5085,7 @@
         <v>52</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -4994,34 +5094,34 @@
       <c r="O13" s="6"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AB13" s="6"/>
       <c r="AC13" s="6" t="s">
@@ -5141,7 +5241,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5175,43 +5275,43 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>6</v>
@@ -5237,25 +5337,25 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>6</v>
@@ -5270,7 +5370,7 @@
         <v>41</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
@@ -5286,7 +5386,7 @@
       <c r="X19" s="6"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
@@ -5296,25 +5396,25 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>40</v>
@@ -5329,7 +5429,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>21</v>
@@ -5346,14 +5446,14 @@
       <c r="U20" s="9"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
@@ -5366,35 +5466,35 @@
         <v>43</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
@@ -5408,7 +5508,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="7"/>
       <c r="W21" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
@@ -5530,7 +5630,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="4"/>
@@ -5568,40 +5668,40 @@
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>6</v>
@@ -5628,22 +5728,22 @@
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>6</v>
@@ -5658,11 +5758,11 @@
         <v>41</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O27" s="6"/>
       <c r="Q27" s="7"/>
@@ -5684,22 +5784,22 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>40</v>
@@ -5714,7 +5814,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>21</v>
@@ -5744,35 +5844,35 @@
         <v>43</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="G29" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -5921,7 +6021,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="R33" s="16"/>
       <c r="S33" s="4"/>
@@ -5941,40 +6041,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M34" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -5986,40 +6086,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB34" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC34" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -6027,22 +6127,22 @@
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>6</v>
@@ -6057,33 +6157,33 @@
         <v>41</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
         <v>8</v>
       </c>
       <c r="R35" s="19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="V35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="W35" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X35" s="19" t="s">
         <v>6</v>
@@ -6101,7 +6201,7 @@
         <v>21</v>
       </c>
       <c r="AC35" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
@@ -6109,22 +6209,22 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>40</v>
@@ -6139,7 +6239,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -6149,25 +6249,25 @@
       </c>
       <c r="O36" s="6"/>
       <c r="Q36" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R36" s="19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="S36" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="V36" s="19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="W36" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="X36" s="19" t="s">
         <v>40</v>
@@ -6182,10 +6282,10 @@
         <v>21</v>
       </c>
       <c r="AB36" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AC36" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -6195,22 +6295,22 @@
         <v>43</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D37" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="G37" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>41</v>
@@ -6219,7 +6319,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -6230,22 +6330,22 @@
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="S37" s="19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T37" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="U37" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="V37" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="U37" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="V37" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="W37" s="19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X37" s="19" t="s">
         <v>41</v>
@@ -6398,7 +6498,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="4"/>
@@ -6415,7 +6515,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R41" s="16"/>
       <c r="S41" s="4"/>
@@ -6479,22 +6579,22 @@
       <c r="H43" s="6"/>
       <c r="I43" s="7"/>
       <c r="J43" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -6502,14 +6602,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -6518,7 +6618,7 @@
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -6526,18 +6626,18 @@
       <c r="E44" s="9"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>21</v>
@@ -6549,17 +6649,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
       <c r="X44" s="9"/>
       <c r="Y44" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -6576,14 +6676,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -6593,17 +6693,17 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -6742,7 +6842,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6778,7 +6878,7 @@
         <v>9</v>
       </c>
       <c r="AA50" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AB50" s="6"/>
       <c r="AC50" s="6"/>
@@ -6808,7 +6908,7 @@
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X51" s="6" t="n">
         <v>4</v>
@@ -6862,7 +6962,7 @@
         <v>3</v>
       </c>
       <c r="AA52" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AB52" s="6"/>
       <c r="AC52" s="6" t="s">
@@ -7104,13 +7204,11 @@
   </sheetData>
   <mergeCells count="178">
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AD3:AE4"/>
     <mergeCell ref="M4:O4"/>
-    <mergeCell ref="AC4:AE4"/>
     <mergeCell ref="L5:O5"/>
-    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="AC5:AE5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
@@ -7123,8 +7221,10 @@
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="S6:S7"/>
     <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:Y7"/>
-    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="Y6:Y7"/>
     <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="N7:O7"/>
@@ -7290,4 +7390,3316 @@
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AE62"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="1" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="4.09"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="17" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="21" style="2" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="30" style="2" width="3.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="5"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="M6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5"/>
+      <c r="Q9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="W10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="6"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="W12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="X13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="11"/>
+      <c r="M14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="5"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="W18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y18" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB18" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE18" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="W19" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB19" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC19" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T20" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U20" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V20" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="W20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y20" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="V21" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="W21" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="X21" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="11"/>
+      <c r="K22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="11"/>
+      <c r="M22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="11"/>
+      <c r="AE22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O23" s="6"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="T26" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="W26" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="X26" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y26" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O27" s="6"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T27" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="W27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="X27" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB27" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC27" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T28" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="W28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y28" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB28" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC28" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T29" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="V29" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="W29" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="X29" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z29" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA29" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="11"/>
+      <c r="M30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="11"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="11"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="11"/>
+      <c r="AE30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O31" s="6"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="5"/>
+      <c r="Q33" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="R33" s="16"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R34" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="S34" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="T34" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="U34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="V34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="W34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="X34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y34" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB34" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC34" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="O35" s="6"/>
+      <c r="Q35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="T35" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="V35" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="W35" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="X35" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y35" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z35" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA35" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB35" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC35" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" s="6"/>
+      <c r="Q36" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="R36" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="S36" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="T36" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="V36" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="W36" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="X36" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y36" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z36" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA36" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB36" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC36" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="Q37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="S37" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="T37" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="U37" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="V37" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="W37" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="X37" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
+      <c r="AA37" s="6"/>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD37" s="6"/>
+      <c r="AE37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L38" s="11"/>
+      <c r="M38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="Q38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="S38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="V38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y38" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB38" s="11"/>
+      <c r="AC38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD38" s="11"/>
+      <c r="AE38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O39" s="6"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="7"/>
+      <c r="AA39" s="6"/>
+      <c r="AB39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="18"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="5"/>
+      <c r="Q41" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="R41" s="16"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="O43" s="6"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="S43" s="6"/>
+      <c r="T43" s="6"/>
+      <c r="U43" s="6"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="6"/>
+      <c r="X43" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y43" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" s="6"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T44" s="6"/>
+      <c r="U44" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="V44" s="6"/>
+      <c r="W44" s="6"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="6"/>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="T45" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="W45" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="6"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L46" s="11"/>
+      <c r="M46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
+      <c r="Y46" s="7"/>
+      <c r="Z46" s="7"/>
+      <c r="AA46" s="6"/>
+      <c r="AB46" s="11"/>
+      <c r="AC46" s="6"/>
+      <c r="AD46" s="11"/>
+      <c r="AE46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O47" s="6"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="7"/>
+      <c r="AA47" s="6"/>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="6"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="13"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="5"/>
+      <c r="Q49" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+      <c r="U50" s="6"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="6"/>
+      <c r="X50" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y50" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z50" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA50" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB50" s="6"/>
+      <c r="AC50" s="6"/>
+      <c r="AD50" s="6"/>
+      <c r="AE50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="6"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="X51" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y51" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z51" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA51" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="6"/>
+      <c r="AD51" s="6"/>
+      <c r="AE51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="9"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z52" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z53" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA53" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB53" s="6"/>
+      <c r="AC53" s="6"/>
+      <c r="AD53" s="6"/>
+      <c r="AE53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7"/>
+      <c r="AA54" s="6"/>
+      <c r="AB54" s="11"/>
+      <c r="AC54" s="6"/>
+      <c r="AD54" s="11"/>
+      <c r="AE54" s="11"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="7"/>
+      <c r="AA55" s="6"/>
+      <c r="AB55" s="6"/>
+      <c r="AC55" s="6"/>
+      <c r="AD55" s="6"/>
+      <c r="AE55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="176">
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="AD10:AE10"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="AD11:AE11"/>
+    <mergeCell ref="AC12:AE12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="AB13:AE13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:Y15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AD14:AE14"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="AD15:AE15"/>
+    <mergeCell ref="N19:O20"/>
+    <mergeCell ref="AD19:AE20"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="U22:Y23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="N27:O28"/>
+    <mergeCell ref="AD27:AE28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="R30:R31"/>
+    <mergeCell ref="S30:S31"/>
+    <mergeCell ref="T30:T31"/>
+    <mergeCell ref="U30:U31"/>
+    <mergeCell ref="V30:W31"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="AD35:AE36"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="Q38:Q39"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="U38:Y39"/>
+    <mergeCell ref="Z38:Z39"/>
+    <mergeCell ref="AA38:AA39"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="AD39:AE39"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="AD42:AE42"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="AD43:AE43"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="AC44:AE44"/>
+    <mergeCell ref="L45:O45"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:I47"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="Q46:Q47"/>
+    <mergeCell ref="R46:R47"/>
+    <mergeCell ref="S46:S47"/>
+    <mergeCell ref="T46:T47"/>
+    <mergeCell ref="U46:Y47"/>
+    <mergeCell ref="Z46:Z47"/>
+    <mergeCell ref="AA46:AA47"/>
+    <mergeCell ref="AD46:AE46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="AD50:AE50"/>
+    <mergeCell ref="N51:O52"/>
+    <mergeCell ref="AD51:AE51"/>
+    <mergeCell ref="AC52:AE52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="AB53:AE53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:I55"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="Q54:Q55"/>
+    <mergeCell ref="R54:R55"/>
+    <mergeCell ref="S54:S55"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="U54:Y55"/>
+    <mergeCell ref="Z54:Z55"/>
+    <mergeCell ref="AA54:AA55"/>
+    <mergeCell ref="AD54:AE54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="AD55:AE55"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>